--- a/PlantPollinatorOffset.xlsx
+++ b/PlantPollinatorOffset.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="992" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="988" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId2"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t xml:space="preserve">TONGUE-TUBE</t>
   </si>
@@ -28,10 +28,7 @@
     <t xml:space="preserve">POLLEN_GRAINS_DEPOSITED</t>
   </si>
   <si>
-    <t xml:space="preserve">NECTAR_VOLUME_CONSUMED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NECTAR_VOLUME_BEFORE</t>
+    <t xml:space="preserve">PERCENT_NECTAR_CONSUMED</t>
   </si>
 </sst>
 </file>
@@ -46,6 +43,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -134,11 +132,11 @@
   <dimension ref="A1:D82"/>
   <sheetFormatPr defaultRowHeight="12.8"/>
   <cols>
-    <col collapsed="false" hidden="false" max="1" min="1" style="0" width="15.9744897959184"/>
-    <col collapsed="false" hidden="false" max="2" min="2" style="0" width="28.3367346938776"/>
-    <col collapsed="false" hidden="false" max="3" min="3" style="0" width="28.2040816326531"/>
-    <col collapsed="false" hidden="false" max="4" min="4" style="0" width="29.030612244898"/>
-    <col collapsed="false" hidden="false" max="1025" min="5" style="0" width="11.5204081632653"/>
+    <col collapsed="false" hidden="false" max="1" min="1" style="0" width="15.6581632653061"/>
+    <col collapsed="false" hidden="false" max="2" min="2" style="0" width="27.6734693877551"/>
+    <col collapsed="false" hidden="false" max="3" min="3" style="0" width="27.5408163265306"/>
+    <col collapsed="false" hidden="false" max="4" min="4" style="0" width="28.2142857142857"/>
+    <col collapsed="false" hidden="false" max="5" min="5" style="0" width="29.5612244897959"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -148,12 +146,10 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="D1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="n">
@@ -163,10 +159,7 @@
         <v>10</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="D2" s="0" t="n">
-        <v>0.544</v>
+        <v>0.882352941176471</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -177,10 +170,7 @@
         <v>8</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>1.702</v>
-      </c>
-      <c r="D3" s="0" t="n">
-        <v>1.766</v>
+        <v>0.963759909399773</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -191,10 +181,7 @@
         <v>7</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>1.344</v>
-      </c>
-      <c r="D4" s="0" t="n">
-        <v>1.648</v>
+        <v>0.815533980582524</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -205,10 +192,7 @@
         <v>6</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>0.528</v>
-      </c>
-      <c r="D5" s="0" t="n">
-        <v>1.216</v>
+        <v>0.43421052631579</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -221,9 +205,6 @@
       <c r="C6" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="0" t="n">
-        <v>1.118</v>
-      </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="n">
@@ -233,10 +214,7 @@
         <v>6</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>0.066</v>
-      </c>
-      <c r="D7" s="0" t="n">
-        <v>0.544</v>
+        <v>0.121323529411765</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -249,9 +227,6 @@
       <c r="C8" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="0" t="n">
-        <v>0.544</v>
-      </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="n">
@@ -261,10 +236,7 @@
         <v>216</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>0.414</v>
-      </c>
-      <c r="D9" s="0" t="n">
-        <v>0.478</v>
+        <v>0.866108786610879</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -275,10 +247,7 @@
         <v>3</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="D10" s="0" t="n">
-        <v>0.544</v>
+        <v>0.882352941176471</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -289,10 +258,7 @@
         <v>71</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>2.808</v>
-      </c>
-      <c r="D11" s="0" t="n">
-        <v>3.166</v>
+        <v>0.886923562855338</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -303,10 +269,7 @@
         <v>106</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>0.378</v>
-      </c>
-      <c r="D12" s="0" t="n">
-        <v>0.544</v>
+        <v>0.694852941176471</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -317,10 +280,7 @@
         <v>127</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>0.288</v>
-      </c>
-      <c r="D13" s="0" t="n">
-        <v>0.416</v>
+        <v>0.692307692307692</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -333,9 +293,6 @@
       <c r="C14" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="0" t="n">
-        <v>0.766</v>
-      </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="n">
@@ -345,10 +302,7 @@
         <v>129</v>
       </c>
       <c r="C15" s="0" t="n">
-        <v>1.656</v>
-      </c>
-      <c r="D15" s="0" t="n">
-        <v>2.014</v>
+        <v>0.822244289970209</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -361,9 +315,6 @@
       <c r="C16" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="D16" s="0" t="n">
-        <v>0.934</v>
-      </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="n">
@@ -373,10 +324,7 @@
         <v>61</v>
       </c>
       <c r="C17" s="0" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="D17" s="0" t="n">
-        <v>0.254</v>
+        <v>0.748031496062992</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -387,10 +335,7 @@
         <v>8</v>
       </c>
       <c r="C18" s="0" t="n">
-        <v>0.174</v>
-      </c>
-      <c r="D18" s="0" t="n">
-        <v>0.478</v>
+        <v>0.364016736401674</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -401,10 +346,7 @@
         <v>117</v>
       </c>
       <c r="C19" s="0" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="D19" s="0" t="n">
-        <v>0.688</v>
+        <v>0.479651162790698</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -417,9 +359,6 @@
       <c r="C20" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="D20" s="0" t="n">
-        <v>0.544</v>
-      </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="n">
@@ -431,9 +370,6 @@
       <c r="C21" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="D21" s="0" t="n">
-        <v>0.848</v>
-      </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="n">
@@ -445,9 +381,6 @@
       <c r="C22" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="D22" s="0" t="n">
-        <v>1.766</v>
-      </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="n">
@@ -459,9 +392,6 @@
       <c r="C23" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="D23" s="0" t="n">
-        <v>2.558</v>
-      </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="n">
@@ -471,10 +401,7 @@
         <v>2</v>
       </c>
       <c r="C24" s="0" t="n">
-        <v>0.414</v>
-      </c>
-      <c r="D24" s="0" t="n">
-        <v>0.478</v>
+        <v>0.866108786610879</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -485,10 +412,7 @@
         <v>104</v>
       </c>
       <c r="C25" s="0" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="D25" s="0" t="n">
-        <v>2.014</v>
+        <v>0.729890764647468</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -499,10 +423,7 @@
         <v>0</v>
       </c>
       <c r="C26" s="0" t="n">
-        <v>0.414</v>
-      </c>
-      <c r="D26" s="0" t="n">
-        <v>0.478</v>
+        <v>0.866108786610879</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -513,10 +434,7 @@
         <v>26</v>
       </c>
       <c r="C27" s="0" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="D27" s="0" t="n">
-        <v>2.014</v>
+        <v>0.968222442899702</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -527,10 +445,7 @@
         <v>1</v>
       </c>
       <c r="C28" s="0" t="n">
-        <v>0.294</v>
-      </c>
-      <c r="D28" s="0" t="n">
-        <v>0.358</v>
+        <v>0.821229050279329</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -541,10 +456,7 @@
         <v>0</v>
       </c>
       <c r="C29" s="0" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="D29" s="0" t="n">
-        <v>2.014</v>
+        <v>0.968222442899702</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -555,10 +467,7 @@
         <v>42</v>
       </c>
       <c r="C30" s="0" t="n">
-        <v>1.584</v>
-      </c>
-      <c r="D30" s="0" t="n">
-        <v>1.648</v>
+        <v>0.961165048543689</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -569,10 +478,7 @@
         <v>108</v>
       </c>
       <c r="C31" s="0" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="D31" s="0" t="n">
-        <v>1.648</v>
+        <v>0.58252427184466</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -583,10 +489,7 @@
         <v>115</v>
       </c>
       <c r="C32" s="0" t="n">
-        <v>3.328</v>
-      </c>
-      <c r="D32" s="0" t="n">
-        <v>4.016</v>
+        <v>0.828685258964143</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -599,9 +502,6 @@
       <c r="C33" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="D33" s="0" t="n">
-        <v>1.216</v>
-      </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="n">
@@ -611,10 +511,7 @@
         <v>122</v>
       </c>
       <c r="C34" s="0" t="n">
-        <v>0.426</v>
-      </c>
-      <c r="D34" s="0" t="n">
-        <v>2.704</v>
+        <v>0.157544378698225</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -625,10 +522,7 @@
         <v>9</v>
       </c>
       <c r="C35" s="0" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="D35" s="0" t="n">
-        <v>0.934</v>
+        <v>0.931477516059957</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -639,10 +533,7 @@
         <v>12</v>
       </c>
       <c r="C36" s="0" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="D36" s="0" t="n">
-        <v>1.534</v>
+        <v>0.958279009126467</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -653,10 +544,7 @@
         <v>4</v>
       </c>
       <c r="C37" s="0" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="D37" s="0" t="n">
-        <v>1.424</v>
+        <v>0.955056179775281</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -667,10 +555,7 @@
         <v>61</v>
       </c>
       <c r="C38" s="0" t="n">
-        <v>0.702</v>
-      </c>
-      <c r="D38" s="0" t="n">
-        <v>1.118</v>
+        <v>0.627906976744186</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -681,10 +566,7 @@
         <v>24</v>
       </c>
       <c r="C39" s="0" t="n">
-        <v>1.224</v>
-      </c>
-      <c r="D39" s="0" t="n">
-        <v>1.318</v>
+        <v>0.928679817905918</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -695,10 +577,7 @@
         <v>83</v>
       </c>
       <c r="C40" s="0" t="n">
-        <v>0.486</v>
-      </c>
-      <c r="D40" s="0" t="n">
-        <v>0.614</v>
+        <v>0.791530944625407</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -709,10 +588,7 @@
         <v>62</v>
       </c>
       <c r="C41" s="0" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="D41" s="0" t="n">
-        <v>2.854</v>
+        <v>0.501051156271899</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -723,10 +599,7 @@
         <v>298</v>
       </c>
       <c r="C42" s="0" t="n">
-        <v>1.152</v>
-      </c>
-      <c r="D42" s="0" t="n">
-        <v>1.766</v>
+        <v>0.652321630804077</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -737,10 +610,7 @@
         <v>209</v>
       </c>
       <c r="C43" s="0" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="D43" s="0" t="n">
-        <v>0.304</v>
+        <v>0.789473684210526</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -751,10 +621,7 @@
         <v>21</v>
       </c>
       <c r="C44" s="0" t="n">
-        <v>1.344</v>
-      </c>
-      <c r="D44" s="0" t="n">
-        <v>2.278</v>
+        <v>0.589991220368745</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -765,10 +632,7 @@
         <v>1</v>
       </c>
       <c r="C45" s="0" t="n">
-        <v>0.754</v>
-      </c>
-      <c r="D45" s="0" t="n">
-        <v>0.848</v>
+        <v>0.889150943396226</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -779,10 +643,7 @@
         <v>5</v>
       </c>
       <c r="C46" s="0" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="D46" s="0" t="n">
-        <v>0.614</v>
+        <v>0.895765472312704</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -793,10 +654,7 @@
         <v>6</v>
       </c>
       <c r="C47" s="0" t="n">
-        <v>0.702</v>
-      </c>
-      <c r="D47" s="0" t="n">
-        <v>0.766</v>
+        <v>0.91644908616188</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -807,10 +665,7 @@
         <v>1</v>
       </c>
       <c r="C48" s="0" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="D48" s="0" t="n">
-        <v>1.424</v>
+        <v>0.955056179775281</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -821,10 +676,7 @@
         <v>5</v>
       </c>
       <c r="C49" s="0" t="n">
-        <v>0.414</v>
-      </c>
-      <c r="D49" s="0" t="n">
-        <v>0.478</v>
+        <v>0.866108786610879</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -835,10 +687,7 @@
         <v>28</v>
       </c>
       <c r="C50" s="0" t="n">
-        <v>0.784</v>
-      </c>
-      <c r="D50" s="0" t="n">
-        <v>0.848</v>
+        <v>0.924528301886793</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -851,9 +700,6 @@
       <c r="C51" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="D51" s="0" t="n">
-        <v>0.688</v>
-      </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="0" t="n">
@@ -865,9 +711,6 @@
       <c r="C52" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="D52" s="0" t="n">
-        <v>0.614</v>
-      </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="0" t="n">
@@ -877,10 +720,7 @@
         <v>0</v>
       </c>
       <c r="C53" s="0" t="n">
-        <v>1.064</v>
-      </c>
-      <c r="D53" s="0" t="n">
-        <v>1.318</v>
+        <v>0.807283763277693</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -891,10 +731,7 @@
         <v>4</v>
       </c>
       <c r="C54" s="0" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="D54" s="0" t="n">
-        <v>3.664</v>
+        <v>0.414847161572052</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -907,9 +744,6 @@
       <c r="C55" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="D55" s="0" t="n">
-        <v>0.614</v>
-      </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="0" t="n">
@@ -919,10 +753,7 @@
         <v>127</v>
       </c>
       <c r="C56" s="0" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="D56" s="0" t="n">
-        <v>0.614</v>
+        <v>0.895765472312704</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -933,10 +764,7 @@
         <v>56</v>
       </c>
       <c r="C57" s="0" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="D57" s="0" t="n">
-        <v>1.534</v>
+        <v>0.645371577574967</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -949,9 +777,6 @@
       <c r="C58" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="D58" s="0" t="n">
-        <v>0.766</v>
-      </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="0" t="n">
@@ -961,10 +786,7 @@
         <v>16</v>
       </c>
       <c r="C59" s="0" t="n">
-        <v>2.494</v>
-      </c>
-      <c r="D59" s="0" t="n">
-        <v>2.558</v>
+        <v>0.974980453479281</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -975,10 +797,7 @@
         <v>23</v>
       </c>
       <c r="C60" s="0" t="n">
-        <v>2.242</v>
-      </c>
-      <c r="D60" s="0" t="n">
-        <v>3.008</v>
+        <v>0.745345744680851</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -989,10 +808,7 @@
         <v>0</v>
       </c>
       <c r="C61" s="0" t="n">
-        <v>0.414</v>
-      </c>
-      <c r="D61" s="0" t="n">
-        <v>0.478</v>
+        <v>0.866108786610879</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1003,10 +819,7 @@
         <v>3</v>
       </c>
       <c r="C62" s="0" t="n">
-        <v>0.352</v>
-      </c>
-      <c r="D62" s="0" t="n">
-        <v>0.416</v>
+        <v>0.846153846153846</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1017,10 +830,7 @@
         <v>0</v>
       </c>
       <c r="C63" s="0" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="D63" s="0" t="n">
-        <v>0.614</v>
+        <v>0.895765472312704</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1031,10 +841,7 @@
         <v>32</v>
       </c>
       <c r="C64" s="0" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="D64" s="0" t="n">
-        <v>0.934</v>
+        <v>0.931477516059957</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1045,10 +852,7 @@
         <v>62</v>
       </c>
       <c r="C65" s="0" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="D65" s="0" t="n">
-        <v>0.544</v>
+        <v>0.882352941176471</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1059,10 +863,7 @@
         <v>2</v>
       </c>
       <c r="C66" s="0" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="D66" s="0" t="n">
-        <v>3.494</v>
+        <v>0.981682884945621</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1073,10 +874,7 @@
         <v>36</v>
       </c>
       <c r="C67" s="0" t="n">
-        <v>1.254</v>
-      </c>
-      <c r="D67" s="0" t="n">
-        <v>1.318</v>
+        <v>0.95144157814871</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1087,10 +885,7 @@
         <v>1</v>
       </c>
       <c r="C68" s="0" t="n">
-        <v>2.214</v>
-      </c>
-      <c r="D68" s="0" t="n">
-        <v>2.278</v>
+        <v>0.971905179982441</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1101,10 +896,7 @@
         <v>57</v>
       </c>
       <c r="C69" s="0" t="n">
-        <v>1.008</v>
-      </c>
-      <c r="D69" s="0" t="n">
-        <v>1.216</v>
+        <v>0.828947368421053</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1115,10 +907,7 @@
         <v>19</v>
       </c>
       <c r="C70" s="0" t="n">
-        <v>1.054</v>
-      </c>
-      <c r="D70" s="0" t="n">
-        <v>1.118</v>
+        <v>0.942754919499106</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1129,10 +918,7 @@
         <v>12</v>
       </c>
       <c r="C71" s="0" t="n">
-        <v>0.638</v>
-      </c>
-      <c r="D71" s="0" t="n">
-        <v>0.766</v>
+        <v>0.83289817232376</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1143,10 +929,7 @@
         <v>24</v>
       </c>
       <c r="C72" s="0" t="n">
-        <v>0.294</v>
-      </c>
-      <c r="D72" s="0" t="n">
-        <v>0.358</v>
+        <v>0.821229050279329</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1157,10 +940,7 @@
         <v>168</v>
       </c>
       <c r="C73" s="0" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="D73" s="0" t="n">
-        <v>1.648</v>
+        <v>0.782766990291262</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1171,10 +951,7 @@
         <v>105</v>
       </c>
       <c r="C74" s="0" t="n">
-        <v>3.774</v>
-      </c>
-      <c r="D74" s="0" t="n">
-        <v>3.838</v>
+        <v>0.983324648254299</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1185,10 +962,7 @@
         <v>16</v>
       </c>
       <c r="C75" s="0" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="D75" s="0" t="n">
-        <v>3.494</v>
+        <v>0.981682884945621</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1199,10 +973,7 @@
         <v>129</v>
       </c>
       <c r="C76" s="0" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="D76" s="0" t="n">
-        <v>2.416</v>
+        <v>0.68294701986755</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1213,10 +984,7 @@
         <v>42</v>
       </c>
       <c r="C77" s="0" t="n">
-        <v>1.584</v>
-      </c>
-      <c r="D77" s="0" t="n">
-        <v>1.648</v>
+        <v>0.961165048543689</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1227,10 +995,7 @@
         <v>12</v>
       </c>
       <c r="C78" s="0" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="D78" s="0" t="n">
-        <v>1.024</v>
+        <v>0.9375</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1241,10 +1006,7 @@
         <v>2</v>
       </c>
       <c r="C79" s="0" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="D79" s="0" t="n">
-        <v>0.934</v>
+        <v>0.931477516059957</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1255,10 +1017,7 @@
         <v>1</v>
       </c>
       <c r="C80" s="0" t="n">
-        <v>1.824</v>
-      </c>
-      <c r="D80" s="0" t="n">
-        <v>1.888</v>
+        <v>0.966101694915254</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1269,10 +1028,7 @@
         <v>48</v>
       </c>
       <c r="C81" s="0" t="n">
-        <v>2.214</v>
-      </c>
-      <c r="D81" s="0" t="n">
-        <v>2.278</v>
+        <v>0.971905179982441</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1283,10 +1039,7 @@
         <v>39</v>
       </c>
       <c r="C82" s="0" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="D82" s="0" t="n">
-        <v>0.934</v>
+        <v>0.931477516059957</v>
       </c>
     </row>
   </sheetData>

--- a/PlantPollinatorOffset.xlsx
+++ b/PlantPollinatorOffset.xlsx
@@ -132,11 +132,12 @@
   <dimension ref="A1:D82"/>
   <sheetFormatPr defaultRowHeight="12.8"/>
   <cols>
-    <col collapsed="false" hidden="false" max="1" min="1" style="0" width="15.6581632653061"/>
-    <col collapsed="false" hidden="false" max="2" min="2" style="0" width="27.6734693877551"/>
-    <col collapsed="false" hidden="false" max="3" min="3" style="0" width="27.5408163265306"/>
-    <col collapsed="false" hidden="false" max="4" min="4" style="0" width="28.2142857142857"/>
-    <col collapsed="false" hidden="false" max="5" min="5" style="0" width="29.5612244897959"/>
+    <col collapsed="false" hidden="false" max="1" min="1" style="0" width="15.5255102040816"/>
+    <col collapsed="false" hidden="false" max="2" min="2" style="0" width="27.4030612244898"/>
+    <col collapsed="false" hidden="false" max="3" min="3" style="0" width="27.2704081632653"/>
+    <col collapsed="false" hidden="false" max="4" min="4" style="0" width="27.8061224489796"/>
+    <col collapsed="false" hidden="false" max="5" min="5" style="0" width="29.1581632653061"/>
+    <col collapsed="false" hidden="false" max="1025" min="6" style="0" width="8.50510204081633"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
